--- a/static/informes/Ae3.xlsx
+++ b/static/informes/Ae3.xlsx
@@ -741,25 +741,25 @@
         <v>139</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>15</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>753</v>
+        <v>803</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>954</v>
+        <v>1054</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>385</v>
+        <v>435</v>
       </c>
       <c r="K12" s="7" t="n"/>
       <c r="L12" s="7" t="n"/>
@@ -933,41 +933,41 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>44</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" s="7" t="n"/>
@@ -991,7 +991,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D18" s="3" t="n"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D19" s="3" t="n"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D20" s="3" t="n"/>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D22" s="3" t="n"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D23" s="3" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D24" s="3" t="n"/>
@@ -1208,29 +1208,29 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>65</v>
+        <v>165</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>15</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>753</v>
+        <v>803</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>954</v>
+        <v>1054</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>385</v>
+        <v>435</v>
       </c>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D26" s="3" t="n"/>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>Aprobado por: admin2</t>
+          <t>Aprobado por: admin</t>
         </is>
       </c>
     </row>
